--- a/11_付费课程/99.资料/闲鱼/闲鱼信息备忘表.xlsx
+++ b/11_付费课程/99.资料/闲鱼/闲鱼信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\闲鱼\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B1A353-4841-4B4C-B675-356188BFC0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554BACE3-EF75-47F9-84C6-4803D60F6610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="59">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -229,6 +229,42 @@
   </si>
   <si>
     <t>59979792</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11719655</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终幻想1—11的琴谱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>76294054</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经典邓丽君曲谱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20765114</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大话三国系列经典Flash游戏</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -840,6 +876,39 @@
         <v>49</v>
       </c>
     </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
     <row r="158" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C158" s="17"/>
     </row>

--- a/11_付费课程/99.资料/闲鱼/闲鱼信息备忘表.xlsx
+++ b/11_付费课程/99.资料/闲鱼/闲鱼信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\闲鱼\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554BACE3-EF75-47F9-84C6-4803D60F6610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D5F9A7-6325-48B4-8E2C-DDA48C750C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="62">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -265,6 +265,17 @@
   </si>
   <si>
     <t>大话三国系列经典Flash游戏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05040112</t>
+  </si>
+  <si>
+    <t>游戏吉他曲谱gp3大合集</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -909,6 +920,17 @@
         <v>56</v>
       </c>
     </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
     <row r="158" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C158" s="17"/>
     </row>

--- a/11_付费课程/99.资料/闲鱼/闲鱼信息备忘表.xlsx
+++ b/11_付费课程/99.资料/闲鱼/闲鱼信息备忘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\闲鱼\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D5F9A7-6325-48B4-8E2C-DDA48C750C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B6FC8D-36A1-41C8-8E4A-C8310AD8DF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3270" yWindow="2400" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="65">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -276,6 +276,17 @@
   </si>
   <si>
     <t>游戏吉他曲谱gp3大合集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>39767823</t>
+  </si>
+  <si>
+    <t>パソコンマナー电脑礼仪PCManner</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -931,6 +942,17 @@
         <v>60</v>
       </c>
     </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="158" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C158" s="17"/>
     </row>

--- a/11_付费课程/99.资料/闲鱼/闲鱼信息备忘表.xlsx
+++ b/11_付费课程/99.资料/闲鱼/闲鱼信息备忘表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Disks\E\Writing\11_付费课程\99.资料\闲鱼\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B6FC8D-36A1-41C8-8E4A-C8310AD8DF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78B9C6C-07D6-4A1E-A722-159805AED844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3270" yWindow="2400" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="68">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -287,6 +287,18 @@
   </si>
   <si>
     <t>パソコンマナー电脑礼仪PCManner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>52570360</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经典游戏金曲200首</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -953,6 +965,17 @@
         <v>63</v>
       </c>
     </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="158" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C158" s="17"/>
     </row>
